--- a/Военные ресурсы ГХС.xlsx
+++ b/Военные ресурсы ГХС.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serge\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serge\Downloads\HHS\HyperHotSeat\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -386,16 +386,16 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>33.834296724470136</c:v>
+                  <c:v>31.699225949133801</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.745664739884393</c:v>
+                  <c:v>27.158127534095094</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.566473988439306</c:v>
+                  <c:v>18.193881312200514</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.8535645472061657</c:v>
+                  <c:v>2.9487652045705861</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -551,13 +551,13 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>27.926298157453935</c:v>
+                  <c:v>27.191188040912667</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>25.514237855946398</c:v>
+                  <c:v>24.358772619984265</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>26.559463986599667</c:v>
+                  <c:v>28.450039339103071</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -839,31 +839,31 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>12.972972972972974</c:v>
+                  <c:v>13.120423467137186</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.427170533365224</c:v>
+                  <c:v>15.717688575209527</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>13.967950251136092</c:v>
+                  <c:v>12.449933833259815</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.5348002870126765</c:v>
+                  <c:v>3.3453903837670929</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.6818942836641959</c:v>
+                  <c:v>11.984119982355537</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.9315953121262854</c:v>
+                  <c:v>7.3259814733127477</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.8117675197321219</c:v>
+                  <c:v>6.4367004852227616</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.692896436259268</c:v>
+                  <c:v>2.8654609616232909</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.9789524037311645</c:v>
+                  <c:v>6.7543008381120426</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1145,31 +1145,31 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>7.9911942762795816</c:v>
+                  <c:v>8.3292328338179384</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.0478811227297733</c:v>
+                  <c:v>9.6354283158130176</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.3307649972482114</c:v>
+                  <c:v>6.4772981435920371</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.9565217391304346</c:v>
+                  <c:v>6.9783046298367255</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.865712713263621</c:v>
+                  <c:v>12.686199955267279</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.843698403962575</c:v>
+                  <c:v>11.236859762916573</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.7490368739680795</c:v>
+                  <c:v>7.4972042048758674</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.352779306549257</c:v>
+                  <c:v>6.835159919481101</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9.8624105668684656</c:v>
+                  <c:v>10.324312234399464</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3959,22 +3959,22 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -3993,19 +3993,19 @@
       </c>
       <c r="P4">
         <f>D4</f>
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="S4">
         <f>25 * (SUM(E4:E4)*$E$40 + SUM(F4:F4)*$F$40 + SUM(G4:G4)*$G$40 + SUM(H4:H4)*$H$40 + SUM(I4:I4)*$I$40 + SUM(J4:J4)*$J$40 + SUM(K4:K4)*$K$40 + SUM(L4:L4)*$L$40 + SUM(M4:M4)*$M$40 + SUM(N4:N4)*$N$40)</f>
-        <v>1950</v>
+        <v>4875</v>
       </c>
       <c r="T4">
         <f>P4+S4</f>
-        <v>21950</v>
+        <v>26875</v>
       </c>
       <c r="U4" s="3">
         <f>T4/$T$8 * 80</f>
-        <v>33.834296724470136</v>
+        <v>31.699225949133801</v>
       </c>
       <c r="V4" t="s">
         <v>14</v>
@@ -4016,7 +4016,7 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -4028,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4037,32 +4037,32 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5">
         <f t="shared" ref="P5:P7" si="0">D5</f>
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="S5">
         <f t="shared" ref="S5:S7" si="1">25 * (SUM(E5:E5)*$E$40 + SUM(F5:F5)*$F$40 + SUM(G5:G5)*$G$40 + SUM(H5:H5)*$H$40 + SUM(I5:I5)*$I$40 + SUM(J5:J5)*$J$40 + SUM(K5:K5)*$K$40 + SUM(L5:L5)*$L$40 + SUM(M5:M5)*$M$40 + SUM(N5:N5)*$N$40)</f>
-        <v>3000</v>
+        <v>5025</v>
       </c>
       <c r="T5">
         <f t="shared" ref="T5:T7" si="2">P5+S5</f>
-        <v>18000</v>
+        <v>23025</v>
       </c>
       <c r="U5" s="3">
         <f t="shared" ref="U5:U7" si="3">T5/$T$8 * 80</f>
-        <v>27.745664739884393</v>
+        <v>27.158127534095094</v>
       </c>
       <c r="V5" t="s">
         <v>15</v>
@@ -4073,10 +4073,10 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -4097,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6">
         <v>4</v>
@@ -4107,19 +4107,19 @@
       </c>
       <c r="P6">
         <f t="shared" si="0"/>
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="S6">
         <f t="shared" si="1"/>
-        <v>2450</v>
+        <v>5425</v>
       </c>
       <c r="T6">
         <f t="shared" si="2"/>
-        <v>9450</v>
+        <v>15425</v>
       </c>
       <c r="U6" s="3">
         <f t="shared" si="3"/>
-        <v>14.566473988439306</v>
+        <v>18.193881312200514</v>
       </c>
       <c r="V6" t="s">
         <v>16</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="U7" s="3">
         <f t="shared" si="3"/>
-        <v>3.8535645472061657</v>
+        <v>2.9487652045705861</v>
       </c>
       <c r="V7" t="s">
         <v>17</v>
@@ -4185,23 +4185,23 @@
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="P8">
         <f>D4+D5+D6+D7</f>
-        <v>44500</v>
+        <v>52500</v>
       </c>
       <c r="Q8">
         <f>SUM(E4:I7)+SUM(K4:N7)</f>
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="R8">
         <f>SUM(E4:N7)</f>
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="S8">
         <f>25 * (SUM(E4:E7)*E40 + SUM(F4:F7)*F40 + SUM(G4:G7)*G40 + SUM(H4:H7)*H40 + SUM(I4:I7)*I40 + SUM(J4:J7)*J40 + SUM(K4:K7)*K40 + SUM(L4:L7)*L40 + SUM(M4:M7)*M40 + SUM(N4:N7)*N40)</f>
-        <v>7400</v>
+        <v>15325</v>
       </c>
       <c r="T8">
         <f>P8+S8</f>
-        <v>51900</v>
+        <v>67825</v>
       </c>
       <c r="U8" s="3">
         <f>T8/$T$8 * 80</f>
@@ -4219,7 +4219,7 @@
         <v>21</v>
       </c>
       <c r="D10">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -4237,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -4249,23 +4249,23 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10">
         <f>D10</f>
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="S10">
         <f>25 * (E10*$E$40 + F10*$F$40 + G10*$G$40 + H10*$H$40 + I10*$I$40 + J10*$J$40 + K10*$K$40 + L10*$L$40 + M10*$M$40 + N10*$N$40)</f>
-        <v>6050</v>
+        <v>7400</v>
       </c>
       <c r="T10">
         <f>P10+S10</f>
-        <v>26050</v>
+        <v>32400</v>
       </c>
       <c r="U10" s="3">
         <f>T10/$T$13 * 80</f>
-        <v>27.926298157453935</v>
+        <v>27.191188040912667</v>
       </c>
       <c r="V10" t="s">
         <v>21</v>
@@ -4276,7 +4276,7 @@
         <v>22</v>
       </c>
       <c r="D11">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="E11">
         <v>9</v>
@@ -4310,19 +4310,19 @@
       </c>
       <c r="P11">
         <f t="shared" ref="P11:P12" si="4">D11</f>
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="S11">
         <f t="shared" ref="S11:S12" si="5">25 * (E11*$E$40 + F11*$F$40 + G11*$G$40 + H11*$H$40 + I11*$I$40 + J11*$J$40 + K11*$K$40 + L11*$L$40 + M11*$M$40 + N11*$N$40)</f>
-        <v>7800</v>
+        <v>8025</v>
       </c>
       <c r="T11">
         <f t="shared" ref="T11:T12" si="6">P11+S11</f>
-        <v>23800</v>
+        <v>29025</v>
       </c>
       <c r="U11" s="3">
         <f t="shared" ref="U11:U13" si="7">T11/$T$13 * 80</f>
-        <v>25.514237855946398</v>
+        <v>24.358772619984265</v>
       </c>
       <c r="V11" t="s">
         <v>22</v>
@@ -4333,19 +4333,19 @@
         <v>23</v>
       </c>
       <c r="D12">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="E12">
+        <v>6</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
         <v>4</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4354,10 +4354,10 @@
         <v>12</v>
       </c>
       <c r="K12">
+        <v>4</v>
+      </c>
+      <c r="L12">
         <v>2</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
       </c>
       <c r="M12">
         <v>8</v>
@@ -4367,19 +4367,19 @@
       </c>
       <c r="P12">
         <f t="shared" si="4"/>
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="S12">
         <f t="shared" si="5"/>
-        <v>4775</v>
+        <v>6900</v>
       </c>
       <c r="T12">
         <f t="shared" si="6"/>
-        <v>24775</v>
+        <v>33900</v>
       </c>
       <c r="U12" s="3">
         <f t="shared" si="7"/>
-        <v>26.559463986599667</v>
+        <v>28.450039339103071</v>
       </c>
       <c r="V12" t="s">
         <v>23</v>
@@ -4388,23 +4388,23 @@
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="P13">
         <f>D10+D11+D12</f>
-        <v>56000</v>
+        <v>73000</v>
       </c>
       <c r="Q13">
         <f>SUM(E10:I12)+SUM(K10:N12)</f>
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="R13">
         <f>SUM(E10:N12)</f>
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="S13">
         <f>SUM(S10:S12)</f>
-        <v>18625</v>
+        <v>22325</v>
       </c>
       <c r="T13">
         <f>P13+S13</f>
-        <v>74625</v>
+        <v>95325</v>
       </c>
       <c r="U13" s="3">
         <f t="shared" si="7"/>
@@ -4428,13 +4428,13 @@
         <v>24</v>
       </c>
       <c r="D16">
-        <v>20000</v>
+        <v>28000</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F16">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -4449,32 +4449,32 @@
         <v>22</v>
       </c>
       <c r="K16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>6</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
       <c r="P16">
         <f>D16</f>
-        <v>20000</v>
+        <v>28000</v>
       </c>
       <c r="S16">
         <f>25 * (E16*$E$40 + F16*$F$40 + G16*$G$40 + H16*$H$40 + I16*$I$40 + J16*$J$40 + K16*$K$40 + L16*$L$40 + M16*$M$40 + N16*$N$40)</f>
-        <v>13900</v>
+        <v>18475</v>
       </c>
       <c r="T16">
         <f t="shared" ref="T16:T35" si="8">P16+S16</f>
-        <v>33900</v>
+        <v>46475</v>
       </c>
       <c r="U16" s="3">
         <f>T16/$T$25 * 80</f>
-        <v>12.972972972972974</v>
+        <v>13.120423467137186</v>
       </c>
       <c r="V16" t="s">
         <v>24</v>
@@ -4485,13 +4485,13 @@
         <v>25</v>
       </c>
       <c r="D17">
-        <v>20000</v>
+        <v>28000</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="F17">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -4500,10 +4500,10 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="K17">
         <v>4</v>
@@ -4512,26 +4512,26 @@
         <v>4</v>
       </c>
       <c r="M17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="P17">
         <f t="shared" ref="P17:P24" si="9">D17</f>
-        <v>20000</v>
+        <v>28000</v>
       </c>
       <c r="S17">
         <f t="shared" ref="S17:S24" si="10">25 * (E17*$E$40 + F17*$F$40 + G17*$G$40 + H17*$H$40 + I17*$I$40 + J17*$J$40 + K17*$K$40 + L17*$L$40 + M17*$M$40 + N17*$N$40)</f>
-        <v>17700</v>
+        <v>27675</v>
       </c>
       <c r="T17">
         <f t="shared" si="8"/>
-        <v>37700</v>
+        <v>55675</v>
       </c>
       <c r="U17" s="3">
         <f t="shared" ref="U17:U25" si="11">T17/$T$25 * 80</f>
-        <v>14.427170533365224</v>
+        <v>15.717688575209527</v>
       </c>
       <c r="V17" t="s">
         <v>25</v>
@@ -4542,10 +4542,10 @@
         <v>26</v>
       </c>
       <c r="D18">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="E18">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F18">
         <v>15</v>
@@ -4566,29 +4566,29 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M18">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N18">
         <v>0</v>
       </c>
       <c r="P18">
         <f t="shared" si="9"/>
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="S18">
         <f t="shared" si="10"/>
-        <v>26500</v>
+        <v>32100</v>
       </c>
       <c r="T18">
         <f t="shared" si="8"/>
-        <v>36500</v>
+        <v>44100</v>
       </c>
       <c r="U18" s="3">
         <f t="shared" si="11"/>
-        <v>13.967950251136092</v>
+        <v>12.449933833259815</v>
       </c>
       <c r="V18" t="s">
         <v>26</v>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="U19" s="3">
         <f t="shared" si="11"/>
-        <v>4.5348002870126765</v>
+        <v>3.3453903837670929</v>
       </c>
       <c r="V19" t="s">
         <v>27</v>
@@ -4656,7 +4656,7 @@
         <v>28</v>
       </c>
       <c r="D20">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="E20">
         <v>6</v>
@@ -4668,10 +4668,10 @@
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J20">
         <v>24</v>
@@ -4690,19 +4690,19 @@
       </c>
       <c r="P20">
         <f t="shared" si="9"/>
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="S20">
         <f t="shared" si="10"/>
-        <v>5300</v>
+        <v>18450</v>
       </c>
       <c r="T20">
         <f t="shared" si="8"/>
-        <v>25300</v>
+        <v>42450</v>
       </c>
       <c r="U20" s="3">
         <f t="shared" si="11"/>
-        <v>9.6818942836641959</v>
+        <v>11.984119982355537</v>
       </c>
       <c r="V20" t="s">
         <v>28</v>
@@ -4713,13 +4713,13 @@
         <v>29</v>
       </c>
       <c r="D21">
-        <v>15500</v>
+        <v>19500</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4728,13 +4728,13 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -4747,19 +4747,19 @@
       </c>
       <c r="P21">
         <f t="shared" si="9"/>
-        <v>15500</v>
+        <v>19500</v>
       </c>
       <c r="S21">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>6450</v>
       </c>
       <c r="T21">
         <f t="shared" si="8"/>
-        <v>15500</v>
+        <v>25950</v>
       </c>
       <c r="U21" s="3">
         <f t="shared" si="11"/>
-        <v>5.9315953121262854</v>
+        <v>7.3259814733127477</v>
       </c>
       <c r="V21" t="s">
         <v>29</v>
@@ -4770,7 +4770,7 @@
         <v>30</v>
       </c>
       <c r="D22">
-        <v>17000</v>
+        <v>22000</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="P22">
         <f t="shared" si="9"/>
-        <v>17000</v>
+        <v>22000</v>
       </c>
       <c r="S22">
         <f t="shared" si="10"/>
@@ -4812,11 +4812,11 @@
       </c>
       <c r="T22">
         <f t="shared" si="8"/>
-        <v>17800</v>
+        <v>22800</v>
       </c>
       <c r="U22" s="3">
         <f t="shared" si="11"/>
-        <v>6.8117675197321219</v>
+        <v>6.4367004852227616</v>
       </c>
       <c r="V22" t="s">
         <v>30</v>
@@ -4839,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4865,15 +4865,15 @@
       </c>
       <c r="S23">
         <f t="shared" si="10"/>
-        <v>1650</v>
+        <v>2150</v>
       </c>
       <c r="T23">
         <f t="shared" si="8"/>
-        <v>9650</v>
+        <v>10150</v>
       </c>
       <c r="U23" s="3">
         <f t="shared" si="11"/>
-        <v>3.692896436259268</v>
+        <v>2.8654609616232909</v>
       </c>
       <c r="V23" t="s">
         <v>31</v>
@@ -4884,7 +4884,7 @@
         <v>32</v>
       </c>
       <c r="D24">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -4896,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -4918,19 +4918,19 @@
       </c>
       <c r="P24">
         <f t="shared" si="9"/>
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="S24">
         <f t="shared" si="10"/>
-        <v>2850</v>
+        <v>3925</v>
       </c>
       <c r="T24">
         <f t="shared" si="8"/>
-        <v>20850</v>
+        <v>23925</v>
       </c>
       <c r="U24" s="3">
         <f t="shared" si="11"/>
-        <v>7.9789524037311645</v>
+        <v>6.7543008381120426</v>
       </c>
       <c r="V24" t="s">
         <v>32</v>
@@ -4939,23 +4939,23 @@
     <row r="25" spans="2:22" x14ac:dyDescent="0.25">
       <c r="P25">
         <f>SUM(D16:D24)</f>
-        <v>137500</v>
+        <v>170500</v>
       </c>
       <c r="Q25">
         <f>SUM(E16:I24)+SUM(K16:N24)</f>
-        <v>225</v>
+        <v>350</v>
       </c>
       <c r="R25">
         <f>SUM(E16:N24)</f>
-        <v>373</v>
+        <v>534</v>
       </c>
       <c r="S25">
         <f>SUM(S16:S24)</f>
-        <v>71550</v>
+        <v>112875</v>
       </c>
       <c r="T25">
         <f t="shared" si="8"/>
-        <v>209050</v>
+        <v>283375</v>
       </c>
       <c r="U25" s="3">
         <f t="shared" si="11"/>
@@ -4973,7 +4973,7 @@
         <v>36</v>
       </c>
       <c r="D27">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="E27">
         <v>5</v>
@@ -5007,19 +5007,19 @@
       </c>
       <c r="P27">
         <f>D27</f>
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="S27">
         <f>25 * (E27*$E$40 + F27*$F$40 + G27*$G$40 + H27*$H$40 + I27*$I$40 + J27*$J$40 + K27*$K$40 + L27*$L$40 + M27*$M$40 + N27*$N$40)</f>
-        <v>14150</v>
+        <v>14275</v>
       </c>
       <c r="T27">
         <f t="shared" si="8"/>
-        <v>18150</v>
+        <v>23275</v>
       </c>
       <c r="U27" s="3">
         <f>T27/$T$36 * 80</f>
-        <v>7.9911942762795816</v>
+        <v>8.3292328338179384</v>
       </c>
       <c r="V27" t="s">
         <v>36</v>
@@ -5030,7 +5030,7 @@
         <v>37</v>
       </c>
       <c r="D28">
-        <v>15500</v>
+        <v>20500</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -5042,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5054,7 +5054,7 @@
         <v>2</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M28">
         <v>4</v>
@@ -5064,19 +5064,19 @@
       </c>
       <c r="P28">
         <f t="shared" ref="P28:P35" si="12">D28</f>
-        <v>15500</v>
+        <v>20500</v>
       </c>
       <c r="S28">
         <f t="shared" ref="S28:S35" si="13">25 * (E28*$E$40 + F28*$F$40 + G28*$G$40 + H28*$H$40 + I28*$I$40 + J28*$J$40 + K28*$K$40 + L28*$L$40 + M28*$M$40 + N28*$N$40)</f>
-        <v>5050</v>
+        <v>6425</v>
       </c>
       <c r="T28">
         <f t="shared" si="8"/>
-        <v>20550</v>
+        <v>26925</v>
       </c>
       <c r="U28" s="3">
         <f t="shared" ref="U28:U36" si="14">T28/$T$36 * 80</f>
-        <v>9.0478811227297733</v>
+        <v>9.6354283158130176</v>
       </c>
       <c r="V28" t="s">
         <v>37</v>
@@ -5108,13 +5108,13 @@
         <v>12</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M29">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5125,15 +5125,15 @@
       </c>
       <c r="S29">
         <f t="shared" si="13"/>
-        <v>4150</v>
+        <v>5600</v>
       </c>
       <c r="T29">
         <f t="shared" si="8"/>
-        <v>16650</v>
+        <v>18100</v>
       </c>
       <c r="U29" s="3">
         <f t="shared" si="14"/>
-        <v>7.3307649972482114</v>
+        <v>6.4772981435920371</v>
       </c>
       <c r="V29" t="s">
         <v>38</v>
@@ -5144,10 +5144,10 @@
         <v>39</v>
       </c>
       <c r="D30">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -5159,7 +5159,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30">
         <v>6</v>
@@ -5178,19 +5178,19 @@
       </c>
       <c r="P30">
         <f t="shared" si="12"/>
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="S30">
         <f t="shared" si="13"/>
-        <v>800</v>
+        <v>2500</v>
       </c>
       <c r="T30">
         <f t="shared" si="8"/>
-        <v>15800</v>
+        <v>19500</v>
       </c>
       <c r="U30" s="3">
         <f t="shared" si="14"/>
-        <v>6.9565217391304346</v>
+        <v>6.9783046298367255</v>
       </c>
       <c r="V30" t="s">
         <v>39</v>
@@ -5201,7 +5201,7 @@
         <v>40</v>
       </c>
       <c r="D31">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -5216,7 +5216,7 @@
         <v>4</v>
       </c>
       <c r="I31">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -5225,29 +5225,29 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N31">
         <v>0</v>
       </c>
       <c r="P31">
         <f t="shared" si="12"/>
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="S31">
         <f t="shared" si="13"/>
-        <v>6950</v>
+        <v>9450</v>
       </c>
       <c r="T31">
         <f t="shared" si="8"/>
-        <v>26950</v>
+        <v>35450</v>
       </c>
       <c r="U31" s="3">
         <f t="shared" si="14"/>
-        <v>11.865712713263621</v>
+        <v>12.686199955267279</v>
       </c>
       <c r="V31" t="s">
         <v>40</v>
@@ -5258,7 +5258,7 @@
         <v>41</v>
       </c>
       <c r="D32">
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="E32">
         <v>10</v>
@@ -5273,7 +5273,7 @@
         <v>4</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J32">
         <v>12</v>
@@ -5292,19 +5292,19 @@
       </c>
       <c r="P32">
         <f t="shared" si="12"/>
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="S32">
         <f t="shared" si="13"/>
-        <v>6900</v>
+        <v>8400</v>
       </c>
       <c r="T32">
         <f t="shared" si="8"/>
-        <v>26900</v>
+        <v>31400</v>
       </c>
       <c r="U32" s="3">
         <f t="shared" si="14"/>
-        <v>11.843698403962575</v>
+        <v>11.236859762916573</v>
       </c>
       <c r="V32" t="s">
         <v>41</v>
@@ -5315,7 +5315,7 @@
         <v>42</v>
       </c>
       <c r="D33">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -5333,35 +5333,35 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K33">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M33">
         <v>6</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P33">
         <f t="shared" si="12"/>
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="S33">
         <f t="shared" si="13"/>
-        <v>5600</v>
+        <v>8450</v>
       </c>
       <c r="T33">
         <f t="shared" si="8"/>
-        <v>17600</v>
+        <v>20950</v>
       </c>
       <c r="U33" s="3">
         <f t="shared" si="14"/>
-        <v>7.7490368739680795</v>
+        <v>7.4972042048758674</v>
       </c>
       <c r="V33" t="s">
         <v>42</v>
@@ -5372,7 +5372,7 @@
         <v>43</v>
       </c>
       <c r="D34">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -5399,26 +5399,26 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N34">
         <v>0</v>
       </c>
       <c r="P34">
         <f t="shared" si="12"/>
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="S34">
         <f t="shared" si="13"/>
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="T34">
         <f t="shared" si="8"/>
-        <v>16700</v>
+        <v>19100</v>
       </c>
       <c r="U34" s="3">
         <f t="shared" si="14"/>
-        <v>7.352779306549257</v>
+        <v>6.835159919481101</v>
       </c>
       <c r="V34" t="s">
         <v>43</v>
@@ -5429,22 +5429,22 @@
         <v>44</v>
       </c>
       <c r="D35">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35">
         <v>3</v>
       </c>
       <c r="H35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35">
         <v>18</v>
@@ -5456,26 +5456,26 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N35">
         <v>0</v>
       </c>
       <c r="P35">
         <f t="shared" si="12"/>
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="S35">
         <f t="shared" si="13"/>
-        <v>7400</v>
+        <v>11850</v>
       </c>
       <c r="T35">
         <f t="shared" si="8"/>
-        <v>22400</v>
+        <v>28850</v>
       </c>
       <c r="U35" s="3">
         <f t="shared" si="14"/>
-        <v>9.8624105668684656</v>
+        <v>10.324312234399464</v>
       </c>
       <c r="V35" t="s">
         <v>44</v>
@@ -5484,23 +5484,23 @@
     <row r="36" spans="3:22" x14ac:dyDescent="0.25">
       <c r="P36">
         <f>SUM(D27:D35)</f>
-        <v>129000</v>
+        <v>154500</v>
       </c>
       <c r="Q36">
         <f>SUM(E27:I35)+SUM(K27:N35)</f>
-        <v>175</v>
+        <v>222</v>
       </c>
       <c r="R36">
         <f>SUM(E27:N35)</f>
-        <v>295</v>
+        <v>348</v>
       </c>
       <c r="S36">
         <f>SUM(S27:S35)</f>
-        <v>52700</v>
+        <v>69050</v>
       </c>
       <c r="T36">
         <f>P36+S36</f>
-        <v>181700</v>
+        <v>223550</v>
       </c>
       <c r="U36" s="3">
         <f t="shared" si="14"/>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="40" spans="3:22" x14ac:dyDescent="0.25">
       <c r="E40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F40">
         <v>4</v>

--- a/Военные ресурсы ГХС.xlsx
+++ b/Военные ресурсы ГХС.xlsx
@@ -839,31 +839,31 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>13.120423467137186</c:v>
+                  <c:v>12.777730045536558</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.717688575209527</c:v>
+                  <c:v>15.307156972248475</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.449933833259815</c:v>
+                  <c:v>12.743362831858407</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.3453903837670929</c:v>
+                  <c:v>3.3542400549875415</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11.984119982355537</c:v>
+                  <c:v>11.671105765100094</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.3259814733127477</c:v>
+                  <c:v>7.1346335595841568</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.4367004852227616</c:v>
+                  <c:v>7.6432683220207922</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.8654609616232909</c:v>
+                  <c:v>2.7906177506658647</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.7543008381120426</c:v>
+                  <c:v>6.57788469799811</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1145,31 +1145,31 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>8.3292328338179384</c:v>
+                  <c:v>9.7567221510883488</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.6354283158130176</c:v>
+                  <c:v>9.5006402048655563</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.4772981435920371</c:v>
+                  <c:v>6.1801109688433629</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.9783046298367255</c:v>
+                  <c:v>6.658130601792573</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12.686199955267279</c:v>
+                  <c:v>12.104139991463935</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11.236859762916573</c:v>
+                  <c:v>10.840802390098165</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.4972042048758674</c:v>
+                  <c:v>7.6653862569355526</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.835159919481101</c:v>
+                  <c:v>6.5215535638070854</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10.324312234399464</c:v>
+                  <c:v>10.772513871105421</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="U16" s="3">
         <f>T16/$T$25 * 80</f>
-        <v>13.120423467137186</v>
+        <v>12.777730045536558</v>
       </c>
       <c r="V16" t="s">
         <v>24</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="U17" s="3">
         <f t="shared" ref="U17:U25" si="11">T17/$T$25 * 80</f>
-        <v>15.717688575209527</v>
+        <v>15.307156972248475</v>
       </c>
       <c r="V17" t="s">
         <v>25</v>
@@ -4551,7 +4551,7 @@
         <v>15</v>
       </c>
       <c r="G18">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H18">
         <v>6</v>
@@ -4580,15 +4580,15 @@
       </c>
       <c r="S18">
         <f t="shared" si="10"/>
-        <v>32100</v>
+        <v>34350</v>
       </c>
       <c r="T18">
         <f t="shared" si="8"/>
-        <v>44100</v>
+        <v>46350</v>
       </c>
       <c r="U18" s="3">
         <f t="shared" si="11"/>
-        <v>12.449933833259815</v>
+        <v>12.743362831858407</v>
       </c>
       <c r="V18" t="s">
         <v>26</v>
@@ -4626,7 +4626,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4637,15 +4637,15 @@
       </c>
       <c r="S19">
         <f t="shared" si="10"/>
-        <v>2850</v>
+        <v>3200</v>
       </c>
       <c r="T19">
         <f t="shared" si="8"/>
-        <v>11850</v>
+        <v>12200</v>
       </c>
       <c r="U19" s="3">
         <f t="shared" si="11"/>
-        <v>3.3453903837670929</v>
+        <v>3.3542400549875415</v>
       </c>
       <c r="V19" t="s">
         <v>27</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="U20" s="3">
         <f t="shared" si="11"/>
-        <v>11.984119982355537</v>
+        <v>11.671105765100094</v>
       </c>
       <c r="V20" t="s">
         <v>28</v>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="U21" s="3">
         <f t="shared" si="11"/>
-        <v>7.3259814733127477</v>
+        <v>7.1346335595841568</v>
       </c>
       <c r="V21" t="s">
         <v>29</v>
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4808,15 +4808,15 @@
       </c>
       <c r="S22">
         <f t="shared" si="10"/>
-        <v>800</v>
+        <v>5800</v>
       </c>
       <c r="T22">
         <f t="shared" si="8"/>
-        <v>22800</v>
+        <v>27800</v>
       </c>
       <c r="U22" s="3">
         <f t="shared" si="11"/>
-        <v>6.4367004852227616</v>
+        <v>7.6432683220207922</v>
       </c>
       <c r="V22" t="s">
         <v>30</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="U23" s="3">
         <f t="shared" si="11"/>
-        <v>2.8654609616232909</v>
+        <v>2.7906177506658647</v>
       </c>
       <c r="V23" t="s">
         <v>31</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="U24" s="3">
         <f t="shared" si="11"/>
-        <v>6.7543008381120426</v>
+        <v>6.57788469799811</v>
       </c>
       <c r="V24" t="s">
         <v>32</v>
@@ -4943,19 +4943,19 @@
       </c>
       <c r="Q25">
         <f>SUM(E16:I24)+SUM(K16:N24)</f>
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="R25">
         <f>SUM(E16:N24)</f>
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="S25">
         <f>SUM(S16:S24)</f>
-        <v>112875</v>
+        <v>120475</v>
       </c>
       <c r="T25">
         <f t="shared" si="8"/>
-        <v>283375</v>
+        <v>290975</v>
       </c>
       <c r="U25" s="3">
         <f t="shared" si="11"/>
@@ -4976,13 +4976,13 @@
         <v>9000</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H27">
         <v>6</v>
@@ -5000,7 +5000,7 @@
         <v>4</v>
       </c>
       <c r="M27">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -5011,15 +5011,15 @@
       </c>
       <c r="S27">
         <f>25 * (E27*$E$40 + F27*$F$40 + G27*$G$40 + H27*$H$40 + I27*$I$40 + J27*$J$40 + K27*$K$40 + L27*$L$40 + M27*$M$40 + N27*$N$40)</f>
-        <v>14275</v>
+        <v>19575</v>
       </c>
       <c r="T27">
         <f t="shared" si="8"/>
-        <v>23275</v>
+        <v>28575</v>
       </c>
       <c r="U27" s="3">
         <f>T27/$T$36 * 80</f>
-        <v>8.3292328338179384</v>
+        <v>9.7567221510883488</v>
       </c>
       <c r="V27" t="s">
         <v>36</v>
@@ -5033,7 +5033,7 @@
         <v>20500</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K28">
         <v>2</v>
@@ -5068,15 +5068,15 @@
       </c>
       <c r="S28">
         <f t="shared" ref="S28:S35" si="13">25 * (E28*$E$40 + F28*$F$40 + G28*$G$40 + H28*$H$40 + I28*$I$40 + J28*$J$40 + K28*$K$40 + L28*$L$40 + M28*$M$40 + N28*$N$40)</f>
-        <v>6425</v>
+        <v>7325</v>
       </c>
       <c r="T28">
         <f t="shared" si="8"/>
-        <v>26925</v>
+        <v>27825</v>
       </c>
       <c r="U28" s="3">
         <f t="shared" ref="U28:U36" si="14">T28/$T$36 * 80</f>
-        <v>9.6354283158130176</v>
+        <v>9.5006402048655563</v>
       </c>
       <c r="V28" t="s">
         <v>37</v>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="U29" s="3">
         <f t="shared" si="14"/>
-        <v>6.4772981435920371</v>
+        <v>6.1801109688433629</v>
       </c>
       <c r="V29" t="s">
         <v>38</v>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="U30" s="3">
         <f t="shared" si="14"/>
-        <v>6.9783046298367255</v>
+        <v>6.658130601792573</v>
       </c>
       <c r="V30" t="s">
         <v>39</v>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="U31" s="3">
         <f t="shared" si="14"/>
-        <v>12.686199955267279</v>
+        <v>12.104139991463935</v>
       </c>
       <c r="V31" t="s">
         <v>40</v>
@@ -5285,7 +5285,7 @@
         <v>2</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5296,15 +5296,15 @@
       </c>
       <c r="S32">
         <f t="shared" si="13"/>
-        <v>8400</v>
+        <v>8750</v>
       </c>
       <c r="T32">
         <f t="shared" si="8"/>
-        <v>31400</v>
+        <v>31750</v>
       </c>
       <c r="U32" s="3">
         <f t="shared" si="14"/>
-        <v>11.236859762916573</v>
+        <v>10.840802390098165</v>
       </c>
       <c r="V32" t="s">
         <v>41</v>
@@ -5345,7 +5345,7 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P33">
         <f t="shared" si="12"/>
@@ -5353,15 +5353,15 @@
       </c>
       <c r="S33">
         <f t="shared" si="13"/>
-        <v>8450</v>
+        <v>9950</v>
       </c>
       <c r="T33">
         <f t="shared" si="8"/>
-        <v>20950</v>
+        <v>22450</v>
       </c>
       <c r="U33" s="3">
         <f t="shared" si="14"/>
-        <v>7.4972042048758674</v>
+        <v>7.6653862569355526</v>
       </c>
       <c r="V33" t="s">
         <v>42</v>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="U34" s="3">
         <f t="shared" si="14"/>
-        <v>6.835159919481101</v>
+        <v>6.5215535638070854</v>
       </c>
       <c r="V34" t="s">
         <v>43</v>
@@ -5438,7 +5438,7 @@
         <v>3</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>8</v>
@@ -5447,7 +5447,7 @@
         <v>2</v>
       </c>
       <c r="J35">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K35">
         <v>3</v>
@@ -5467,15 +5467,15 @@
       </c>
       <c r="S35">
         <f t="shared" si="13"/>
-        <v>11850</v>
+        <v>14550</v>
       </c>
       <c r="T35">
         <f t="shared" si="8"/>
-        <v>28850</v>
+        <v>31550</v>
       </c>
       <c r="U35" s="3">
         <f t="shared" si="14"/>
-        <v>10.324312234399464</v>
+        <v>10.772513871105421</v>
       </c>
       <c r="V35" t="s">
         <v>44</v>
@@ -5488,19 +5488,19 @@
       </c>
       <c r="Q36">
         <f>SUM(E27:I35)+SUM(K27:N35)</f>
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="R36">
         <f>SUM(E27:N35)</f>
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="S36">
         <f>SUM(S27:S35)</f>
-        <v>69050</v>
+        <v>79800</v>
       </c>
       <c r="T36">
         <f>P36+S36</f>
-        <v>223550</v>
+        <v>234300</v>
       </c>
       <c r="U36" s="3">
         <f t="shared" si="14"/>
